--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Personnes&amp;Responsable_fichier" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="75">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t xml:space="preserve">HOBO_n°38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMS4_n°0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_n°0</t>
   </si>
   <si>
     <t xml:space="preserve">description_recolteur</t>
@@ -247,10 +253,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -339,7 +344,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -365,10 +370,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -559,11 +560,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
@@ -732,11 +732,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J85"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.38"/>
@@ -810,7 +809,7 @@
       <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -824,7 +823,7 @@
       <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -838,7 +837,7 @@
       <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -852,7 +851,7 @@
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -866,7 +865,7 @@
       <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -880,7 +879,7 @@
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -894,7 +893,7 @@
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -908,7 +907,7 @@
       <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -922,7 +921,7 @@
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -936,7 +935,7 @@
       <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -950,7 +949,7 @@
       <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -964,7 +963,7 @@
       <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -978,7 +977,7 @@
       <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -992,7 +991,7 @@
       <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1006,7 +1005,7 @@
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1020,7 +1019,7 @@
       <c r="C20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1034,7 +1033,7 @@
       <c r="C21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1048,7 +1047,7 @@
       <c r="C22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1062,7 +1061,7 @@
       <c r="C23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1076,7 +1075,7 @@
       <c r="C24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1090,7 +1089,7 @@
       <c r="C25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1104,7 +1103,7 @@
       <c r="C26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1118,7 +1117,7 @@
       <c r="C27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1132,7 +1131,7 @@
       <c r="C28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1146,7 +1145,7 @@
       <c r="C29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1160,7 +1159,7 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1174,7 +1173,7 @@
       <c r="C31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1188,7 +1187,7 @@
       <c r="C32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1202,7 +1201,7 @@
       <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1216,7 +1215,7 @@
       <c r="C34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1230,7 +1229,7 @@
       <c r="C35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1244,7 +1243,7 @@
       <c r="C36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1258,7 +1257,7 @@
       <c r="C37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1272,7 +1271,7 @@
       <c r="C38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1286,7 +1285,7 @@
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1300,7 +1299,7 @@
       <c r="C40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1314,7 +1313,7 @@
       <c r="C41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1328,7 +1327,7 @@
       <c r="C42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="6" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -1342,7 +1341,7 @@
       <c r="C43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="7"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -1354,7 +1353,7 @@
       <c r="C44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="7"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
@@ -1366,7 +1365,7 @@
       <c r="C45" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="7"/>
+      <c r="D45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
@@ -1378,7 +1377,7 @@
       <c r="C46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="7"/>
+      <c r="D46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
@@ -1390,7 +1389,7 @@
       <c r="C47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="7"/>
+      <c r="D47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
@@ -1402,7 +1401,7 @@
       <c r="C48" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="7"/>
+      <c r="D48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
@@ -1414,7 +1413,7 @@
       <c r="C49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D49" s="7"/>
+      <c r="D49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
@@ -1426,7 +1425,7 @@
       <c r="C50" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="D50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
@@ -1438,7 +1437,7 @@
       <c r="C51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="7"/>
+      <c r="D51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
@@ -1450,7 +1449,7 @@
       <c r="C52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="7"/>
+      <c r="D52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
@@ -1462,7 +1461,7 @@
       <c r="C53" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="7"/>
+      <c r="D53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
@@ -1474,7 +1473,7 @@
       <c r="C54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D54" s="7"/>
+      <c r="D54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
@@ -1486,7 +1485,7 @@
       <c r="C55" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D55" s="7"/>
+      <c r="D55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
@@ -1498,7 +1497,7 @@
       <c r="C56" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D56" s="7"/>
+      <c r="D56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
@@ -1510,7 +1509,7 @@
       <c r="C57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D57" s="7"/>
+      <c r="D57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
@@ -1522,7 +1521,7 @@
       <c r="C58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="7"/>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
@@ -1534,7 +1533,7 @@
       <c r="C59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="7"/>
+      <c r="D59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
@@ -1546,7 +1545,7 @@
       <c r="C60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="7"/>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -1558,7 +1557,7 @@
       <c r="C61" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="7"/>
+      <c r="D61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
@@ -1570,7 +1569,7 @@
       <c r="C62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D62" s="7"/>
+      <c r="D62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
@@ -1582,7 +1581,7 @@
       <c r="C63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D63" s="7"/>
+      <c r="D63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
@@ -1594,7 +1593,7 @@
       <c r="C64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D64" s="7"/>
+      <c r="D64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
@@ -1606,7 +1605,7 @@
       <c r="C65" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D65" s="7"/>
+      <c r="D65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
@@ -1618,7 +1617,7 @@
       <c r="C66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D66" s="7"/>
+      <c r="D66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
@@ -1630,7 +1629,7 @@
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D67" s="7"/>
+      <c r="D67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
@@ -1642,7 +1641,7 @@
       <c r="C68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D68" s="7"/>
+      <c r="D68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
@@ -1654,7 +1653,7 @@
       <c r="C69" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D69" s="7"/>
+      <c r="D69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
@@ -1666,7 +1665,7 @@
       <c r="C70" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D70" s="7"/>
+      <c r="D70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
@@ -1678,7 +1677,7 @@
       <c r="C71" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D71" s="7"/>
+      <c r="D71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
@@ -1690,7 +1689,7 @@
       <c r="C72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D72" s="7"/>
+      <c r="D72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
@@ -1702,7 +1701,7 @@
       <c r="C73" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="7"/>
+      <c r="D73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
@@ -1714,7 +1713,7 @@
       <c r="C74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D74" s="7"/>
+      <c r="D74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
@@ -1726,7 +1725,7 @@
       <c r="C75" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D75" s="7"/>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
@@ -1738,7 +1737,7 @@
       <c r="C76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D76" s="7"/>
+      <c r="D76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
@@ -1750,7 +1749,7 @@
       <c r="C77" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D77" s="7"/>
+      <c r="D77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
@@ -1762,7 +1761,7 @@
       <c r="C78" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D78" s="7"/>
+      <c r="D78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
@@ -1774,7 +1773,7 @@
       <c r="C79" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D79" s="7"/>
+      <c r="D79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -1786,22 +1785,62 @@
       <c r="C80" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D80" s="7"/>
+      <c r="D80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D81" s="7"/>
+      <c r="A81" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>45352</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D82" s="7"/>
+      <c r="A82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D83" s="7"/>
+      <c r="A83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>45352</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D84" s="7"/>
+      <c r="A84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D85" s="7"/>
+      <c r="D85" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1884,6 +1923,10 @@
     <hyperlink ref="A78" r:id="rId77" display="marine.zwicke@umontpellier.fr"/>
     <hyperlink ref="A79" r:id="rId78" display="marine.zwicke@umontpellier.fr"/>
     <hyperlink ref="A80" r:id="rId79" display="marine.zwicke@umontpellier.fr"/>
+    <hyperlink ref="A81" r:id="rId80" display="marine.zwicke@umontpellier.fr"/>
+    <hyperlink ref="A82" r:id="rId81" display="marine.zwicke@umontpellier.fr"/>
+    <hyperlink ref="A83" r:id="rId82" display="marine.zwicke@umontpellier.fr"/>
+    <hyperlink ref="A84" r:id="rId83" display="marine.zwicke@umontpellier.fr"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1898,14 +1941,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.97"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1913,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -1922,7 +1964,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1930,7 +1972,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_personnes.xlsx
@@ -234,10 +234,10 @@
     <t xml:space="preserve">HOBO_n°38</t>
   </si>
   <si>
-    <t xml:space="preserve">TMS4_n°0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dendro_n°0</t>
+    <t xml:space="preserve">TMS4_95224601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_92261195</t>
   </si>
   <si>
     <t xml:space="preserve">description_recolteur</t>
@@ -257,7 +257,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -300,6 +300,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -344,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -370,6 +376,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1791,7 +1801,7 @@
       <c r="A81" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -1805,7 +1815,7 @@
       <c r="A82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -1817,7 +1827,7 @@
       <c r="A83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -1831,7 +1841,7 @@
       <c r="A84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C84" s="1" t="s">
